--- a/data/file_generation/input/data_81/七年级标准.xlsx
+++ b/data/file_generation/input/data_81/七年级标准.xlsx
@@ -1557,26 +1557,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7211E540-8A59-472D-AA06-F2C5CE76C29F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE272FA5-2334-49EB-8929-3C0898F5128D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0EBC758-3EA8-4D2E-AF0A-6C8CA6FC7E83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88784226-D39E-4643-B745-3A38484AB404}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79130399-56EB-4804-AFF4-85A9F2BB1203}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EDB3F50-34D5-4DFD-B8D5-5C3C24362E65}"/>
 </file>